--- a/sampleprojects/CorporateTax/excel/states/IN_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/IN_corp.xlsx
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts, no transaction count as of Jan 1, 2024); result.in_gross_receipts is greater than or equal to result.in_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.in_gross_receipts &gt;= result.in_economic_nexus_threshold</t>
+    <t>in_result.gross_receipts &gt;= in_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.in_has_nexus = true;</t>
+    <t>set in_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.in_has_nexus = false; set result.in_tax_liability = 0.0;</t>
+    <t>set in_result.has_nexus = false; set in_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate IN Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Indiana nexus</t>
   </si>
   <si>
-    <t>result.in_has_nexus is equal to true</t>
+    <t>in_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Indiana state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.in_state_additions = 0.0; if result.in_out_of_state_muni_interest != 0.0 then set result.in_state_additions = result.in_state_additions + result.in_out_of_state_muni_interest; endif set result.in_state_subtractions = 0.0; if result.in_municipal_interest != 0.0 then set result.in_state_subtractions = result.in_state_subtractions + result.in_municipal_interest; endif if result.in_state_taxes_paid != 0.0 then set result.in_state_subtractions = result.in_state_subtractions + result.in_state_taxes_paid; endif add (("Indiana additions: $" + string value of (result.in_state_additions)) + ", subtractions: $") + string value of (result.in_state_subtractions) to job.audit_trail;</t>
+    <t>set in_result.state_additions = 0.0; if in_result.out_of_state_muni_interest != 0.0 then set in_result.state_additions = in_result.state_additions + in_result.out_of_state_muni_interest; endif set in_result.state_subtractions = 0.0; if in_result.municipal_interest != 0.0 then set in_result.state_subtractions = in_result.state_subtractions + in_result.municipal_interest; endif if in_result.state_taxes_paid != 0.0 then set in_result.state_subtractions = in_result.state_subtractions + in_result.state_taxes_paid; endif add (("Indiana additions: $" + string value of (in_result.state_additions)) + ", subtractions: $") + string value of (in_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.in_state_additions = 0.0; set result.in_state_subtractions = 0.0;</t>
+    <t>set in_result.state_additions = 0.0; set in_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate IN State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.in_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.in_apportioned_income &gt; 0.0</t>
+    <t>in_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Indiana corporate tax (flat rate 4.9%); Apply Indiana 4.9% flat rate</t>
   </si>
   <si>
-    <t>set result.in_taxable_income = the maximum of (result.in_apportioned_income + result.in_state_additions - result.in_state_subtractions) and (0.0); set result.in_tax_liability = the maximum of (result.in_taxable_income * result.in_corp_tax_rate - result.in_state_credits) and (0.0); set result.in_refund_or_owed = result.in_estimated_payments - result.in_tax_liability; add "Indiana taxable income: $" + string value of (result.in_taxable_income) to job.audit_trail; add "Indiana tax liability (4.9%): $" + string value of (result.in_tax_liability) to job.audit_trail;</t>
+    <t>set in_result.taxable_income = the maximum of (in_result.apportioned_income + in_result.state_additions - in_result.state_subtractions) and (0.0); set in_result.tax_liability = the maximum of (in_result.taxable_income * in_result.corp_tax_rate - in_result.state_credits) and (0.0); set in_result.refund_or_owed = in_result.estimated_payments - in_result.tax_liability; add "Indiana taxable income: $" + string value of (in_result.taxable_income) to job.audit_trail; add "Indiana tax liability (4.9%): $" + string value of (in_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.in_taxable_income = 0.0; set result.in_tax_liability = 0.0;</t>
+    <t>set in_result.taxable_income = 0.0; set in_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,13 +205,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>in_result</t>
   </si>
   <si>
     <t>(17 attributes)</t>
   </si>
   <si>
-    <t>in_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -226,7 +226,7 @@
     <t>Declared from decision-table usage; referenced by IN but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>in_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -238,7 +238,7 @@
     <t>IN uses single-sales factor apportionment (100% sales)</t>
   </si>
   <si>
-    <t>in_corp_tax_rate</t>
+    <t>corp_tax_rate</t>
   </si>
   <si>
     <t>0.049</t>
@@ -247,7 +247,7 @@
     <t>IN corporate income tax rate: 4.9% flat rate (2025, Indiana Code § 6-3-2-1)</t>
   </si>
   <si>
-    <t>in_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -256,13 +256,13 @@
     <t>IN economic nexus gross receipts threshold: $100,000 (transaction threshold removed Jan 1, 2024)</t>
   </si>
   <si>
-    <t>in_estimated_payments</t>
-  </si>
-  <si>
-    <t>in_gross_receipts</t>
-  </si>
-  <si>
-    <t>in_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -274,49 +274,49 @@
     <t>Whether corporation has nexus with Indiana</t>
   </si>
   <si>
-    <t>in_municipal_interest</t>
-  </si>
-  <si>
-    <t>in_out_of_state_muni_interest</t>
-  </si>
-  <si>
-    <t>in_refund_or_owed</t>
-  </si>
-  <si>
-    <t>in_state_additions</t>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>out_of_state_muni_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>state_additions</t>
   </si>
   <si>
     <t>IN additions to federal taxable income (out-of-state municipal bond interest acquired after 12/31/2011, certain expenses, etc.)</t>
   </si>
   <si>
-    <t>in_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>IN tax credits (economic development, R&amp;D, headquarters relocation, neighborhood assistance, etc.)</t>
   </si>
   <si>
-    <t>in_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>IN subtractions from federal taxable income (IN municipal bond interest, state income taxes, state NOL, etc.)</t>
   </si>
   <si>
-    <t>in_state_taxes_paid</t>
-  </si>
-  <si>
-    <t>in_tax_liability</t>
+    <t>state_taxes_paid</t>
+  </si>
+  <si>
+    <t>tax_liability</t>
   </si>
   <si>
     <t>IN corporate income tax liability</t>
   </si>
   <si>
-    <t>in_taxable_income</t>
+    <t>taxable_income</t>
   </si>
   <si>
     <t>IN taxable income after apportionment and modifications</t>
   </si>
   <si>
-    <t>in_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
